--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -182,7 +182,7 @@
     <t>long</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -209,19 +209,19 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_1000000;1980000_10</t>
+    <t>1990000_2985000|1010301_2</t>
   </si>
   <si>
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_10000000;1980000_15</t>
+    <t>1990000_14985000|1010301_10</t>
   </si>
   <si>
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_100000000;1980000_20</t>
+    <t>1990000_44985000|1010301_30</t>
   </si>
 </sst>
 </file>
@@ -1337,10 +1337,10 @@
         <v>199</v>
       </c>
       <c r="E5" s="5">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F5" s="5">
-        <v>1000000</v>
+        <v>2985000</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>19</v>
@@ -1366,7 +1366,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>10000000</v>
+        <v>14985000</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>21</v>
@@ -1390,10 +1390,10 @@
         <v>2999</v>
       </c>
       <c r="E7" s="1">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>100000000</v>
+        <v>44985000</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>23</v>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>序列ID</t>
   </si>
@@ -176,6 +176,9 @@
     <t>重置时间(天)</t>
   </si>
   <si>
+    <t>初始金币</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -188,7 +191,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
+    <t>type</t>
   </si>
   <si>
     <t>pay</t>
@@ -197,13 +200,16 @@
     <t>weight</t>
   </si>
   <si>
-    <t>fullup</t>
-  </si>
-  <si>
-    <t>getitem</t>
-  </si>
-  <si>
-    <t>resetime</t>
+    <t>fullUp</t>
+  </si>
+  <si>
+    <t>getItem</t>
+  </si>
+  <si>
+    <t>reseTime</t>
+  </si>
+  <si>
+    <t>baseGold</t>
   </si>
   <si>
     <t>小罐子</t>
@@ -410,7 +416,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,6 +426,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,7 +754,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -766,16 +778,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -784,89 +796,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -883,6 +895,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1234,12 +1249,13 @@
     <col min="6" max="6" width="12.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="9" style="1"/>
+    <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1264,56 +1280,65 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>18</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1322,8 +1347,9 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1331,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5">
         <v>199</v>
@@ -1343,10 +1369,13 @@
         <v>2985000</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H5">
         <v>3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>100000</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1357,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5">
         <v>999</v>
@@ -1369,10 +1398,13 @@
         <v>14985000</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>3</v>
+      </c>
+      <c r="I6" s="1">
+        <v>300000</v>
       </c>
       <c r="K6"/>
     </row>
@@ -1384,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5">
         <v>2999</v>
@@ -1396,10 +1428,13 @@
         <v>44985000</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>800000</v>
       </c>
       <c r="K7"/>
     </row>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1DA067-276C-4C61-86F9-2F67E2150888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -27,18 +33,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -47,6 +54,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,13 +64,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -71,6 +80,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -78,13 +88,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -93,6 +104,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -100,13 +112,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -115,6 +128,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -123,13 +137,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -138,6 +153,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -150,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>序列ID</t>
   </si>
@@ -228,19 +244,17 @@
   </si>
   <si>
     <t>1990000_44985000|1010301_30</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,171 +266,38 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,204 +306,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -630,255 +331,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -891,71 +350,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1233,14 +645,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
@@ -1255,7 +667,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1280,11 +692,11 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1293,7 +705,7 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
@@ -1307,11 +719,11 @@
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1334,11 +746,11 @@
       <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1347,28 +759,28 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="5">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="1">
         <v>199</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="1">
         <v>1500</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="1">
         <v>2985000</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H5">
@@ -1378,17 +790,17 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="1">
         <v>999</v>
       </c>
       <c r="E6" s="1">
@@ -1397,7 +809,7 @@
       <c r="F6" s="1">
         <v>14985000</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H6">
@@ -1408,17 +820,17 @@
       </c>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="1">
         <v>2999</v>
       </c>
       <c r="E7" s="1">
@@ -1427,7 +839,7 @@
       <c r="F7" s="1">
         <v>44985000</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H7">
@@ -1438,79 +850,60 @@
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="5"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="G9" s="5"/>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="G10" s="5"/>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="G11" s="5"/>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K11"/>
     </row>
-    <row r="12" spans="11:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="5"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K13"/>
     </row>
-    <row r="14" spans="11:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K14"/>
     </row>
-    <row r="15" spans="11:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K15"/>
     </row>
-    <row r="16" spans="11:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K16"/>
     </row>
-    <row r="17" spans="11:11">
+    <row r="17" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K17"/>
     </row>
-    <row r="18" spans="11:11">
+    <row r="18" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K18"/>
     </row>
-    <row r="19" spans="11:11">
+    <row r="19" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K19"/>
     </row>
-    <row r="20" spans="11:11">
+    <row r="20" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K20"/>
     </row>
-    <row r="21" spans="11:11">
+    <row r="21" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K21"/>
     </row>
-    <row r="22" spans="11:11">
+    <row r="22" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K22"/>
     </row>
-    <row r="23" spans="11:11">
+    <row r="23" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K23"/>
     </row>
-    <row r="24" spans="11:11">
+    <row r="24" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K24"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1DA067-276C-4C61-86F9-2F67E2150888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -33,19 +27,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -54,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -64,14 +56,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -80,7 +71,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -88,14 +78,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -104,7 +93,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -112,14 +100,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -128,7 +115,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -137,14 +123,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -153,7 +138,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -198,6 +182,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -244,17 +231,19 @@
   </si>
   <si>
     <t>1990000_44985000|1010301_30</t>
-  </si>
-  <si>
-    <t>BigDecimal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,38 +255,171 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,24 +428,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -331,13 +633,270 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -350,24 +909,74 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -645,14 +1254,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
@@ -667,7 +1276,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -692,11 +1301,11 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -704,53 +1313,53 @@
         <v>9</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I3" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -759,29 +1368,29 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1">
-        <v>199</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="E5" s="6">
         <v>1500</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="6">
         <v>2985000</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -790,18 +1399,18 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:11">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1">
-        <v>999</v>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="6">
+        <v>9.99</v>
       </c>
       <c r="E6" s="1">
         <v>3500</v>
@@ -809,8 +1418,8 @@
       <c r="F6" s="1">
         <v>14985000</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
+      <c r="G6" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -820,18 +1429,18 @@
       </c>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:11">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2999</v>
+      <c r="C7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6">
+        <v>29.99</v>
       </c>
       <c r="E7" s="1">
         <v>5000</v>
@@ -839,8 +1448,8 @@
       <c r="F7" s="1">
         <v>44985000</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>25</v>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -850,60 +1459,79 @@
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
+      <c r="A8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="G8" s="6"/>
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="G9" s="6"/>
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
+      <c r="A10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="G11" s="6"/>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="11:11">
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
+      <c r="A13" s="6"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="11:11">
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="11:11">
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="11:11">
       <c r="K16"/>
     </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:11">
       <c r="K17"/>
     </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:11">
       <c r="K18"/>
     </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="11:11">
       <c r="K19"/>
     </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="11:11">
       <c r="K20"/>
     </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="11:11">
       <c r="K21"/>
     </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="11:11">
       <c r="K22"/>
     </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="11:11">
       <c r="K23"/>
     </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="11:11">
       <c r="K24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>序列ID</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
   </si>
   <si>
     <t>long</t>
@@ -437,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor rgb="FFF6C6AC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,12 +625,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -754,7 +772,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -766,34 +784,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -878,7 +896,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -889,6 +907,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -897,7 +918,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1301,7 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1292,50 +1313,50 @@
         <v>9</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6" t="s">
         <v>19</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1347,29 +1368,29 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="6"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="5">
-        <v>199</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="E5" s="6">
         <v>1500</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <v>2985000</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>21</v>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -1379,17 +1400,17 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="5">
-        <v>999</v>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="6">
+        <v>9.99</v>
       </c>
       <c r="E6" s="1">
         <v>3500</v>
@@ -1397,8 +1418,8 @@
       <c r="F6" s="1">
         <v>14985000</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>23</v>
+      <c r="G6" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -1409,17 +1430,17 @@
       <c r="K6"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5">
-        <v>2999</v>
+      <c r="C7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6">
+        <v>29.99</v>
       </c>
       <c r="E7" s="1">
         <v>5000</v>
@@ -1427,8 +1448,8 @@
       <c r="F7" s="1">
         <v>44985000</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>25</v>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -1439,40 +1460,40 @@
       <c r="K7"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="G8" s="6"/>
       <c r="K8"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="G9" s="6"/>
       <c r="K9"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="K10"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="G11" s="6"/>
       <c r="K11"/>
     </row>
     <row r="12" spans="11:11">
       <c r="K12"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="5"/>
+      <c r="A13" s="6"/>
       <c r="K13"/>
     </row>
     <row r="14" spans="11:11">

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -96,7 +96,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-金币</t>
+金币上限 = 领取金币 - 初始金币</t>
         </r>
       </text>
     </comment>
@@ -1387,7 +1387,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="6">
-        <v>2985000</v>
+        <v>2885000</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>22</v>
@@ -1416,7 +1416,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>14985000</v>
+        <v>14685000</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>24</v>
@@ -1446,7 +1446,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>44985000</v>
+        <v>44185000</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>26</v>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -218,19 +218,19 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_2985000|1010301_2</t>
+    <t>1990000_796000|1010301_1</t>
   </si>
   <si>
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_14985000|1010301_10</t>
+    <t>1990000_3997000|1010302_2</t>
   </si>
   <si>
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_44985000|1010301_30</t>
+    <t>1990000_11997000|1010303_2</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1387,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="6">
-        <v>2885000</v>
+        <v>796000</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>22</v>
@@ -1396,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>100000</v>
+        <v>99500</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1416,7 +1416,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>14685000</v>
+        <v>3997000</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>24</v>
@@ -1425,7 +1425,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>300000</v>
+        <v>499500</v>
       </c>
       <c r="K6"/>
     </row>
@@ -1446,7 +1446,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>44185000</v>
+        <v>11997000</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>26</v>
@@ -1455,7 +1455,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>800000</v>
+        <v>1499500</v>
       </c>
       <c r="K7"/>
     </row>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB74709-C019-4D3F-9EA1-E83D33DE0F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -78,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -100,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -123,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -150,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>序列ID</t>
   </si>
@@ -231,19 +237,25 @@
   </si>
   <si>
     <t>1990000_11997000|1010303_2</t>
+  </si>
+  <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
+    <t>1_1|2_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,150 +276,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -418,8 +286,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,13 +302,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,188 +318,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -648,255 +342,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -912,71 +364,24 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1254,14 +659,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
@@ -1271,12 +676,12 @@
     <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
+    <col min="10" max="10" width="21.375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1301,11 +706,14 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1328,11 +736,14 @@
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1355,11 +766,14 @@
       <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1368,28 +782,28 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6">
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="1">
         <v>1.99</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="1">
         <v>1500</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="1">
         <v>796000</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H5">
@@ -1398,18 +812,21 @@
       <c r="I5" s="1">
         <v>99500</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="6">
+      <c r="J5" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="1">
         <v>9.99</v>
       </c>
       <c r="E6" s="1">
@@ -1418,7 +835,7 @@
       <c r="F6" s="1">
         <v>3997000</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H6">
@@ -1427,19 +844,22 @@
       <c r="I6" s="1">
         <v>499500</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="1">
         <v>29.99</v>
       </c>
       <c r="E7" s="1">
@@ -1448,7 +868,7 @@
       <c r="F7" s="1">
         <v>11997000</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H7">
@@ -1457,81 +877,65 @@
       <c r="I7" s="1">
         <v>1499500</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="G8" s="6"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="G9" s="6"/>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="G10" s="6"/>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="G11" s="6"/>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K11"/>
     </row>
-    <row r="12" spans="11:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K13"/>
     </row>
-    <row r="14" spans="11:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K14"/>
     </row>
-    <row r="15" spans="11:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K15"/>
     </row>
-    <row r="16" spans="11:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K16"/>
     </row>
-    <row r="17" spans="11:11">
+    <row r="17" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K17"/>
     </row>
-    <row r="18" spans="11:11">
+    <row r="18" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K18"/>
     </row>
-    <row r="19" spans="11:11">
+    <row r="19" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K19"/>
     </row>
-    <row r="20" spans="11:11">
+    <row r="20" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K20"/>
     </row>
-    <row r="21" spans="11:11">
+    <row r="21" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K21"/>
     </row>
-    <row r="22" spans="11:11">
+    <row r="22" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K22"/>
     </row>
-    <row r="23" spans="11:11">
+    <row r="23" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K23"/>
     </row>
-    <row r="24" spans="11:11">
+    <row r="24" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K24"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -145,12 +145,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>序列ID</t>
   </si>
@@ -179,6 +202,9 @@
     <t>初始金币</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -191,6 +217,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -215,22 +244,34 @@
     <t>baseGold</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_2985000|1010301_2</t>
+    <t>1990000_796000|1010301_1</t>
+  </si>
+  <si>
+    <t>1_google199|2_ios199</t>
   </si>
   <si>
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_14985000|1010301_10</t>
+    <t>1990000_3997000|1010302_2</t>
+  </si>
+  <si>
+    <t>1_google999|2_ios999</t>
   </si>
   <si>
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_44985000|1010301_30</t>
+    <t>1990000_11997000|1010303_2</t>
+  </si>
+  <si>
+    <t>1_google2499|2_ios2499</t>
   </si>
 </sst>
 </file>
@@ -419,7 +460,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,12 +470,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +807,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -796,16 +831,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -814,89 +849,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -906,20 +941,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1271,12 +1300,12 @@
     <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
+    <col min="10" max="10" width="21.375" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1301,62 +1330,71 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1368,132 +1406,122 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
         <v>1.99</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="1">
         <v>1500</v>
       </c>
-      <c r="F5" s="6">
-        <v>2885000</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>22</v>
+      <c r="F5" s="1">
+        <v>796000</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>100000</v>
+        <v>99500</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="6">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1">
         <v>9.99</v>
       </c>
       <c r="E6" s="1">
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>14685000</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>24</v>
+        <v>3997000</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>300000</v>
+        <v>499500</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="K6"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="6">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="6">
-        <v>29.99</v>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
+        <v>24.99</v>
       </c>
       <c r="E7" s="1">
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>44185000</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>26</v>
+        <v>11997000</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>800000</v>
+        <v>1249500</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="G8" s="6"/>
+    <row r="8" spans="11:11">
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="G9" s="6"/>
+    <row r="9" spans="11:11">
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="G10" s="6"/>
+    <row r="10" spans="11:11">
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="G11" s="6"/>
+    <row r="11" spans="11:11">
       <c r="K11"/>
     </row>
     <row r="12" spans="11:11">
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6"/>
+    <row r="13" spans="11:11">
       <c r="K13"/>
     </row>
     <row r="14" spans="11:11">

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB74709-C019-4D3F-9EA1-E83D33DE0F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,12 +145,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>序列ID</t>
   </si>
@@ -185,6 +202,9 @@
     <t>初始金币</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -197,6 +217,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -221,41 +244,47 @@
     <t>baseGold</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>小罐子</t>
   </si>
   <si>
     <t>1990000_796000|1010301_1</t>
   </si>
   <si>
+    <t>1_google199|2_ios199</t>
+  </si>
+  <si>
     <t>中罐子</t>
   </si>
   <si>
     <t>1990000_3997000|1010302_2</t>
   </si>
   <si>
+    <t>1_google999|2_ios999</t>
+  </si>
+  <si>
     <t>大罐子</t>
   </si>
   <si>
     <t>1990000_11997000|1010303_2</t>
   </si>
   <si>
-    <t>渠道商品ID</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-  </si>
-  <si>
-    <t>channelCommodity</t>
-  </si>
-  <si>
-    <t>1_1|2_2</t>
+    <t>1_google2499|2_ios2499</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +303,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -286,14 +459,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,13 +469,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,8 +479,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -342,13 +683,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -358,30 +941,71 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -659,14 +1283,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
@@ -676,12 +1300,12 @@
     <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.375" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -706,74 +1330,74 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -782,9 +1406,9 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -792,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1">
         <v>1.99</v>
@@ -804,7 +1428,7 @@
         <v>796000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -813,10 +1437,10 @@
         <v>99500</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -824,7 +1448,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1">
         <v>9.99</v>
@@ -836,7 +1460,7 @@
         <v>3997000</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -845,11 +1469,11 @@
         <v>499500</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -857,10 +1481,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1">
-        <v>29.99</v>
+        <v>24.99</v>
       </c>
       <c r="E7" s="1">
         <v>5000</v>
@@ -869,73 +1493,73 @@
         <v>11997000</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>1499500</v>
+        <v>1249500</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="11:11">
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="11:11">
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="11:11">
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="11:11">
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="11:11">
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="11:11">
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="11:11">
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="11:11">
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="11:11">
       <c r="K16"/>
     </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:11">
       <c r="K17"/>
     </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:11">
       <c r="K18"/>
     </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="11:11">
       <c r="K19"/>
     </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="11:11">
       <c r="K20"/>
     </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="11:11">
       <c r="K21"/>
     </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="11:11">
       <c r="K22"/>
     </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="11:11">
       <c r="K23"/>
     </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="11:11">
       <c r="K24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_796000|1010301_1</t>
+    <t>1990000_5572000|1010301_1</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_3997000|1010302_2</t>
+    <t>1990000_27979000|1010302_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_11997000|1010303_2</t>
+    <t>1990000_83979000|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -1305,7 +1305,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1408,7 +1408,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>99500</v>
+        <v>696500</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>26</v>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>499500</v>
+        <v>3496500</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>29</v>
@@ -1499,38 +1499,38 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>1249500</v>
+        <v>8746500</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K7"/>
     </row>
-    <row r="8" spans="11:11">
+    <row r="8" spans="1:11">
       <c r="K8"/>
     </row>
-    <row r="9" spans="11:11">
+    <row r="9" spans="1:11">
       <c r="K9"/>
     </row>
-    <row r="10" spans="11:11">
+    <row r="10" spans="1:11">
       <c r="K10"/>
     </row>
-    <row r="11" spans="11:11">
+    <row r="11" spans="1:11">
       <c r="K11"/>
     </row>
-    <row r="12" spans="11:11">
+    <row r="12" spans="1:11">
       <c r="K12"/>
     </row>
-    <row r="13" spans="11:11">
+    <row r="13" spans="1:11">
       <c r="K13"/>
     </row>
-    <row r="14" spans="11:11">
+    <row r="14" spans="1:11">
       <c r="K14"/>
     </row>
-    <row r="15" spans="11:11">
+    <row r="15" spans="1:11">
       <c r="K15"/>
     </row>
-    <row r="16" spans="11:11">
+    <row r="16" spans="1:11">
       <c r="K16"/>
     </row>
     <row r="17" spans="11:11">

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_5572000|1010301_1</t>
+    <t>1990000_5546000|1010301_1</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_27979000|1010302_2</t>
+    <t>1990000_27911000|1010302_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_83979000|1010303_2</t>
+    <t>1990000_83891000|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -1425,7 +1425,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="1">
-        <v>796000</v>
+        <v>5546000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1457,7 +1457,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>3997000</v>
+        <v>27911000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>28</v>
@@ -1490,7 +1490,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>11997000</v>
+        <v>83891000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_5546000|1010301_1</t>
+    <t>1990000_5546000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_27911000|1010302_2</t>
+    <t>1990000_27911000</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_83891000|1010303_2</t>
+    <t>1990000_83891000</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -1297,10 +1297,10 @@
     <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_5546000</t>
+    <t>1990000_179000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_27911000</t>
+    <t>1990000_899000</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_83891000</t>
+    <t>1990000_2699000</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -1425,7 +1425,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="1">
-        <v>5546000</v>
+        <v>179000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1434,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>696500</v>
+        <v>8950</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>26</v>
@@ -1457,7 +1457,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>27911000</v>
+        <v>899000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>28</v>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>3496500</v>
+        <v>89900</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>29</v>
@@ -1490,7 +1490,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>83891000</v>
+        <v>2699000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
@@ -1499,7 +1499,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>8746500</v>
+        <v>350870</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_179000</t>
+    <t>1990000_5546000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_899000</t>
+    <t>1990000_27911000</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_2699000</t>
+    <t>1990000_83891000</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -1425,7 +1425,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="1">
-        <v>179000</v>
+        <v>5546000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1434,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>8950</v>
+        <v>696500</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>26</v>
@@ -1457,7 +1457,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>899000</v>
+        <v>27911000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>28</v>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>89900</v>
+        <v>3496500</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>29</v>
@@ -1490,7 +1490,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>2699000</v>
+        <v>83891000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
@@ -1499,7 +1499,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>350870</v>
+        <v>8746500</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_179000</t>
+    <t>1990000_597000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_899000</t>
+    <t>1990000_2997000</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_2699000</t>
+    <t>1990000_8997000</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -449,12 +449,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1425,7 +1425,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="1">
-        <v>179000</v>
+        <v>597000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1434,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>8950</v>
+        <v>29850</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>26</v>
@@ -1457,7 +1457,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>899000</v>
+        <v>2997000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>28</v>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>89900</v>
+        <v>299700</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>29</v>
@@ -1490,7 +1490,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>2699000</v>
+        <v>8997000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
@@ -1499,7 +1499,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>350870</v>
+        <v>1169610</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>

--- a/slots/resources/sample/PiggyBank.xlsx
+++ b/slots/resources/sample/PiggyBank.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PiggyBank" sheetId="1" r:id="rId1"/>
@@ -250,7 +250,7 @@
     <t>小罐子</t>
   </si>
   <si>
-    <t>1990000_5546000</t>
+    <t>1990000_597000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -259,7 +259,7 @@
     <t>中罐子</t>
   </si>
   <si>
-    <t>1990000_27911000</t>
+    <t>1990000_2997000</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
@@ -268,7 +268,7 @@
     <t>大罐子</t>
   </si>
   <si>
-    <t>1990000_83891000</t>
+    <t>1990000_8997000</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -449,12 +449,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1425,7 +1425,7 @@
         <v>1500</v>
       </c>
       <c r="F5" s="1">
-        <v>5546000</v>
+        <v>597000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1434,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>696500</v>
+        <v>29850</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>26</v>
@@ -1457,7 +1457,7 @@
         <v>3500</v>
       </c>
       <c r="F6" s="1">
-        <v>27911000</v>
+        <v>2997000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>28</v>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>3496500</v>
+        <v>299700</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>29</v>
@@ -1490,7 +1490,7 @@
         <v>5000</v>
       </c>
       <c r="F7" s="1">
-        <v>83891000</v>
+        <v>8997000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
@@ -1499,7 +1499,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>8746500</v>
+        <v>1169610</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>
